--- a/notebooks/XGBoost/skr_predictions_comparison_2019.xlsx
+++ b/notebooks/XGBoost/skr_predictions_comparison_2019.xlsx
@@ -490,7 +490,7 @@
         <v>2019</v>
       </c>
       <c r="C2" t="n">
-        <v>1.557040572166443</v>
+        <v>1.56466269493103</v>
       </c>
       <c r="D2" t="n">
         <v>1.47</v>
@@ -499,16 +499,16 @@
         <v>1.579</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0870405721664429</v>
+        <v>-0.0946626949310303</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0870405721664429</v>
+        <v>0.0946626949310303</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.921127358261422</v>
+        <v>-6.439639110954443</v>
       </c>
       <c r="I2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>2019</v>
       </c>
       <c r="C3" t="n">
-        <v>1.651973485946655</v>
+        <v>1.667132258415222</v>
       </c>
       <c r="D3" t="n">
         <v>1.524</v>
@@ -535,16 +535,16 @@
         <v>1.639</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1279734859466553</v>
+        <v>-0.1431322584152221</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1279734859466553</v>
+        <v>0.1431322584152221</v>
       </c>
       <c r="H3" t="n">
-        <v>-8.397210363953757</v>
+        <v>-9.391880473439773</v>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
         <v>2019</v>
       </c>
       <c r="C4" t="n">
-        <v>1.661346912384033</v>
+        <v>1.675092935562134</v>
       </c>
       <c r="D4" t="n">
         <v>1.608</v>
@@ -571,16 +571,16 @@
         <v>1.679</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05334691238403311</v>
+        <v>-0.06709293556213369</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05334691238403311</v>
+        <v>0.06709293556213369</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.317594053733402</v>
+        <v>-4.172446241426225</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         <v>2019</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7008376121521</v>
+        <v>1.723139762878418</v>
       </c>
       <c r="D5" t="n">
         <v>1.666</v>
@@ -607,20 +607,20 @@
         <v>1.71</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.03483761215209968</v>
+        <v>-0.05713976287841804</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03483761215209968</v>
+        <v>0.05713976287841804</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.091093166392538</v>
+        <v>-3.429757675775393</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Отличная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
         <v>2019</v>
       </c>
       <c r="C6" t="n">
-        <v>1.320851445198059</v>
+        <v>1.318114876747131</v>
       </c>
       <c r="D6" t="n">
         <v>1.287</v>
@@ -643,13 +643,13 @@
         <v>1.358</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.03385144519805916</v>
+        <v>-0.03111487674713143</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03385144519805916</v>
+        <v>0.03111487674713143</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.630259922149119</v>
+        <v>-2.417628340880453</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
@@ -670,7 +670,7 @@
         <v>2019</v>
       </c>
       <c r="C7" t="n">
-        <v>1.367264151573181</v>
+        <v>1.387471914291382</v>
       </c>
       <c r="D7" t="n">
         <v>1.319</v>
@@ -679,20 +679,20 @@
         <v>1.428</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0482641515731812</v>
+        <v>-0.06847191429138189</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0482641515731812</v>
+        <v>0.06847191429138189</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.659147200392813</v>
+        <v>-5.191198960680962</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Отличная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         <v>2019</v>
       </c>
       <c r="C8" t="n">
-        <v>1.440750956535339</v>
+        <v>1.419993758201599</v>
       </c>
       <c r="D8" t="n">
         <v>1.324</v>
@@ -715,20 +715,20 @@
         <v>1.459</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1167509565353393</v>
+        <v>-0.09599375820159906</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1167509565353393</v>
+        <v>0.09599375820159906</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.818048076687257</v>
+        <v>-7.25028385208452</v>
       </c>
       <c r="I8" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Удовлетворительная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
         <v>2019</v>
       </c>
       <c r="C9" t="n">
-        <v>1.320715069770813</v>
+        <v>1.32001793384552</v>
       </c>
       <c r="D9" t="n">
         <v>1.239</v>
@@ -751,13 +751,13 @@
         <v>1.349</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08171506977081289</v>
+        <v>-0.08101793384551992</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08171506977081289</v>
+        <v>0.08101793384551992</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.59524372645786</v>
+        <v>-6.538977711502818</v>
       </c>
       <c r="I9" t="n">
         <v>45</v>
@@ -778,7 +778,7 @@
         <v>2019</v>
       </c>
       <c r="C10" t="n">
-        <v>1.615504026412964</v>
+        <v>1.580164313316345</v>
       </c>
       <c r="D10" t="n">
         <v>1.512</v>
@@ -787,20 +787,20 @@
         <v>1.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1035040264129639</v>
+        <v>-0.0681643133163452</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1035040264129639</v>
+        <v>0.0681643133163452</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.845504392391789</v>
+        <v>-4.508221780181561</v>
       </c>
       <c r="I10" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Удовлетворительная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
         <v>2019</v>
       </c>
       <c r="C11" t="n">
-        <v>1.30826723575592</v>
+        <v>1.30204164981842</v>
       </c>
       <c r="D11" t="n">
         <v>1.257</v>
@@ -823,20 +823,20 @@
         <v>1.33</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05126723575592051</v>
+        <v>-0.04504164981842051</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05126723575592051</v>
+        <v>0.04504164981842051</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.078539041839342</v>
+        <v>-3.583265697567265</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Отличная</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>2019</v>
       </c>
       <c r="C12" t="n">
-        <v>1.814493536949158</v>
+        <v>1.816671967506409</v>
       </c>
       <c r="D12" t="n">
         <v>1.707</v>
@@ -859,16 +859,16 @@
         <v>1.821</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1074935369491576</v>
+        <v>-0.1096719675064086</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1074935369491576</v>
+        <v>0.1096719675064086</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.297219504930148</v>
+        <v>-6.424836995103024</v>
       </c>
       <c r="I12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>2019</v>
       </c>
       <c r="C13" t="n">
-        <v>1.809015035629272</v>
+        <v>1.813644409179688</v>
       </c>
       <c r="D13" t="n">
         <v>1.762</v>
@@ -895,20 +895,20 @@
         <v>1.801</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.04701503562927245</v>
+        <v>-0.05164440917968749</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04701503562927245</v>
+        <v>0.05164440917968749</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.668276709947358</v>
+        <v>-2.931010736645147</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Отличная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
         <v>2019</v>
       </c>
       <c r="C14" t="n">
-        <v>1.449626922607422</v>
+        <v>1.445921421051025</v>
       </c>
       <c r="D14" t="n">
         <v>1.374</v>
@@ -931,13 +931,13 @@
         <v>1.496</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07562692260742176</v>
+        <v>-0.07192142105102528</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07562692260742176</v>
+        <v>0.07192142105102528</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.504142838968105</v>
+        <v>-5.234455680569526</v>
       </c>
       <c r="I14" t="n">
         <v>39</v>
@@ -958,7 +958,7 @@
         <v>2019</v>
       </c>
       <c r="C15" t="n">
-        <v>1.833578944206238</v>
+        <v>1.834986925125122</v>
       </c>
       <c r="D15" t="n">
         <v>1.758</v>
@@ -967,16 +967,16 @@
         <v>1.854</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07557894420623779</v>
+        <v>-0.07698692512512206</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07557894420623779</v>
+        <v>0.07698692512512206</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.29914358397257</v>
+        <v>-4.379233511099093</v>
       </c>
       <c r="I15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>2019</v>
       </c>
       <c r="C16" t="n">
-        <v>1.546903729438782</v>
+        <v>1.555153965950012</v>
       </c>
       <c r="D16" t="n">
         <v>1.436</v>
@@ -1003,16 +1003,16 @@
         <v>1.548</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1109037294387818</v>
+        <v>-0.1191539659500123</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1109037294387818</v>
+        <v>0.1191539659500123</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.723100935848315</v>
+        <v>-8.297629940808655</v>
       </c>
       <c r="I16" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>2019</v>
       </c>
       <c r="C17" t="n">
-        <v>1.45850670337677</v>
+        <v>1.485837578773499</v>
       </c>
       <c r="D17" t="n">
         <v>1.375</v>
@@ -1039,20 +1039,20 @@
         <v>1.499</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08350670337677002</v>
+        <v>-0.1108375787734985</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08350670337677002</v>
+        <v>0.1108375787734985</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.073214791037819</v>
+        <v>-8.060914819890803</v>
       </c>
       <c r="I17" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Удовлетворительная</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
         <v>2019</v>
       </c>
       <c r="C18" t="n">
-        <v>1.520330190658569</v>
+        <v>1.525550484657288</v>
       </c>
       <c r="D18" t="n">
         <v>1.359</v>
@@ -1075,16 +1075,16 @@
         <v>1.527</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1613301906585694</v>
+        <v>-0.1665504846572876</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1613301906585694</v>
+        <v>0.1665504846572876</v>
       </c>
       <c r="H18" t="n">
-        <v>-11.87124287406691</v>
+        <v>-12.25537046779158</v>
       </c>
       <c r="I18" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>2019</v>
       </c>
       <c r="C19" t="n">
-        <v>1.673434734344482</v>
+        <v>1.667214035987854</v>
       </c>
       <c r="D19" t="n">
         <v>1.665</v>
@@ -1111,16 +1111,16 @@
         <v>1.65</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.008434734344482386</v>
+        <v>-0.002214035987853968</v>
       </c>
       <c r="G19" t="n">
-        <v>0.008434734344482386</v>
+        <v>0.002214035987853968</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5065906513202634</v>
+        <v>-0.1329751344056438</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>2019</v>
       </c>
       <c r="C20" t="n">
-        <v>1.374676942825317</v>
+        <v>1.392211079597473</v>
       </c>
       <c r="D20" t="n">
         <v>1.423</v>
@@ -1147,16 +1147,16 @@
         <v>1.385</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04832305717468266</v>
+        <v>0.0307889204025269</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04832305717468266</v>
+        <v>0.0307889204025269</v>
       </c>
       <c r="H20" t="n">
-        <v>3.39585784783434</v>
+        <v>2.163662712756634</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>2019</v>
       </c>
       <c r="C21" t="n">
-        <v>1.458690404891968</v>
+        <v>1.445818424224854</v>
       </c>
       <c r="D21" t="n">
         <v>1.389</v>
@@ -1183,16 +1183,16 @@
         <v>1.48</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.06969040489196776</v>
+        <v>-0.0568184242248535</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06969040489196776</v>
+        <v>0.0568184242248535</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.017307767600271</v>
+        <v>-4.090599296245752</v>
       </c>
       <c r="I21" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>2019</v>
       </c>
       <c r="C22" t="n">
-        <v>1.704192280769348</v>
+        <v>1.699603199958801</v>
       </c>
       <c r="D22" t="n">
         <v>1.609</v>
@@ -1219,16 +1219,16 @@
         <v>1.699</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.09519228076934816</v>
+        <v>-0.09060319995880128</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09519228076934816</v>
+        <v>0.09060319995880128</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.916238705366573</v>
+        <v>-5.631025479105114</v>
       </c>
       <c r="I22" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>2019</v>
       </c>
       <c r="C23" t="n">
-        <v>1.725882291793823</v>
+        <v>1.729016542434692</v>
       </c>
       <c r="D23" t="n">
         <v>1.703</v>
@@ -1255,16 +1255,16 @@
         <v>1.737</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.02288229179382317</v>
+        <v>-0.02601654243469231</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02288229179382317</v>
+        <v>0.02601654243469231</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.343646024299658</v>
+        <v>-1.527688927462849</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>2019</v>
       </c>
       <c r="C24" t="n">
-        <v>1.681484460830688</v>
+        <v>1.674628973007202</v>
       </c>
       <c r="D24" t="n">
         <v>1.608</v>
@@ -1291,16 +1291,16 @@
         <v>1.663</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.07348446083068838</v>
+        <v>-0.06662897300720205</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07348446083068838</v>
+        <v>0.06662897300720205</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.569929156137337</v>
+        <v>-4.143592848706596</v>
       </c>
       <c r="I24" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>1.60088038444519</v>
+        <v>1.576755881309509</v>
       </c>
       <c r="D25" t="n">
         <v>1.495</v>
@@ -1327,20 +1327,20 @@
         <v>1.597</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1058803844451903</v>
+        <v>-0.08175588130950917</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1058803844451903</v>
+        <v>0.08175588130950917</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.082299962888984</v>
+        <v>-5.468620823378539</v>
       </c>
       <c r="I25" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Удовлетворительная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>1.881815671920776</v>
+        <v>1.918652892112732</v>
       </c>
       <c r="D26" t="n">
         <v>1.786</v>
@@ -1363,20 +1363,20 @@
         <v>1.899</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.09581567192077634</v>
+        <v>-0.1326528921127319</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09581567192077634</v>
+        <v>0.1326528921127319</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.364819256482437</v>
+        <v>-7.427373578540419</v>
       </c>
       <c r="I26" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Удовлетворительная</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
         <v>2019</v>
       </c>
       <c r="C27" t="n">
-        <v>1.419035792350769</v>
+        <v>1.425171852111816</v>
       </c>
       <c r="D27" t="n">
         <v>1.351</v>
@@ -1399,16 +1399,16 @@
         <v>1.447</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.06803579235076906</v>
+        <v>-0.07417185211181643</v>
       </c>
       <c r="G27" t="n">
-        <v>0.06803579235076906</v>
+        <v>0.07417185211181643</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.035957983032499</v>
+        <v>-5.490144493842815</v>
       </c>
       <c r="I27" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>2019</v>
       </c>
       <c r="C28" t="n">
-        <v>1.233610033988953</v>
+        <v>1.218228816986084</v>
       </c>
       <c r="D28" t="n">
         <v>0.981</v>
@@ -1435,13 +1435,13 @@
         <v>1.035</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2526100339889527</v>
+        <v>-0.237228816986084</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2526100339889527</v>
+        <v>0.237228816986084</v>
       </c>
       <c r="H28" t="n">
-        <v>-25.750258306723</v>
+        <v>-24.18234627788828</v>
       </c>
       <c r="I28" t="n">
         <v>83</v>
@@ -1462,7 +1462,7 @@
         <v>2019</v>
       </c>
       <c r="C29" t="n">
-        <v>1.389216661453247</v>
+        <v>1.387871980667114</v>
       </c>
       <c r="D29" t="n">
         <v>1.338</v>
@@ -1471,20 +1471,20 @@
         <v>1.442</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.05121666145324699</v>
+        <v>-0.04987198066711418</v>
       </c>
       <c r="G29" t="n">
-        <v>0.05121666145324699</v>
+        <v>0.04987198066711418</v>
       </c>
       <c r="H29" t="n">
-        <v>-3.827852126550598</v>
+        <v>-3.727352815180432</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Отличная</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
         <v>2019</v>
       </c>
       <c r="C30" t="n">
-        <v>1.455205082893372</v>
+        <v>1.425623178482056</v>
       </c>
       <c r="D30" t="n">
         <v>1.377</v>
@@ -1507,20 +1507,20 @@
         <v>1.46</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.07820508289337158</v>
+        <v>-0.04862317848205566</v>
       </c>
       <c r="G30" t="n">
-        <v>0.07820508289337158</v>
+        <v>0.04862317848205566</v>
       </c>
       <c r="H30" t="n">
-        <v>-5.679381473737951</v>
+        <v>-3.531095024114427</v>
       </c>
       <c r="I30" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Отличная</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>2019</v>
       </c>
       <c r="C31" t="n">
-        <v>1.377755522727966</v>
+        <v>1.359143257141113</v>
       </c>
       <c r="D31" t="n">
         <v>1.233</v>
@@ -1543,16 +1543,16 @@
         <v>1.391</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1447555227279662</v>
+        <v>-0.1261432571411132</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1447555227279662</v>
+        <v>0.1261432571411132</v>
       </c>
       <c r="H31" t="n">
-        <v>-11.74010727720731</v>
+        <v>-10.23059668622167</v>
       </c>
       <c r="I31" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>2019</v>
       </c>
       <c r="C32" t="n">
-        <v>1.578585624694824</v>
+        <v>1.568953275680542</v>
       </c>
       <c r="D32" t="n">
         <v>1.506</v>
@@ -1579,16 +1579,16 @@
         <v>1.572</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.07258562469482421</v>
+        <v>-0.06295327568054199</v>
       </c>
       <c r="G32" t="n">
-        <v>0.07258562469482421</v>
+        <v>0.06295327568054199</v>
       </c>
       <c r="H32" t="n">
-        <v>-4.819762595937862</v>
+        <v>-4.180164387818193</v>
       </c>
       <c r="I32" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>2019</v>
       </c>
       <c r="C33" t="n">
-        <v>2.088363170623779</v>
+        <v>2.089099168777466</v>
       </c>
       <c r="D33" t="n">
         <v>2.073</v>
@@ -1615,16 +1615,16 @@
         <v>2.118</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.01536317062377934</v>
+        <v>-0.01609916877746587</v>
       </c>
       <c r="G33" t="n">
-        <v>0.01536317062377934</v>
+        <v>0.01609916877746587</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7411080860482075</v>
+        <v>-0.7766120973210742</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>2019</v>
       </c>
       <c r="C34" t="n">
-        <v>1.464036226272583</v>
+        <v>1.469109773635864</v>
       </c>
       <c r="D34" t="n">
         <v>1.389</v>
@@ -1651,16 +1651,16 @@
         <v>1.488</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.075036226272583</v>
+        <v>-0.08010977363586425</v>
       </c>
       <c r="G34" t="n">
-        <v>0.075036226272583</v>
+        <v>0.08010977363586425</v>
       </c>
       <c r="H34" t="n">
-        <v>-5.402176117536573</v>
+        <v>-5.767442306397714</v>
       </c>
       <c r="I34" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>2019</v>
       </c>
       <c r="C35" t="n">
-        <v>1.560937404632568</v>
+        <v>1.543864369392395</v>
       </c>
       <c r="D35" t="n">
         <v>1.443</v>
@@ -1687,16 +1687,16 @@
         <v>1.561</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1179374046325683</v>
+        <v>-0.100864369392395</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1179374046325683</v>
+        <v>0.100864369392395</v>
       </c>
       <c r="H35" t="n">
-        <v>-8.173070314107298</v>
+        <v>-6.989907788800759</v>
       </c>
       <c r="I35" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>2019</v>
       </c>
       <c r="C36" t="n">
-        <v>1.5789635181427</v>
+        <v>1.586430668830872</v>
       </c>
       <c r="D36" t="n">
         <v>1.506</v>
@@ -1723,16 +1723,16 @@
         <v>1.582</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.07296351814270019</v>
+        <v>-0.08043066883087158</v>
       </c>
       <c r="G36" t="n">
-        <v>0.07296351814270019</v>
+        <v>0.08043066883087158</v>
       </c>
       <c r="H36" t="n">
-        <v>-4.84485512235725</v>
+        <v>-5.340681861279653</v>
       </c>
       <c r="I36" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>2019</v>
       </c>
       <c r="C37" t="n">
-        <v>1.669564843177795</v>
+        <v>1.669690489768982</v>
       </c>
       <c r="D37" t="n">
         <v>1.555</v>
@@ -1759,16 +1759,16 @@
         <v>1.651</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1145648431777955</v>
+        <v>-0.114690489768982</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1145648431777955</v>
+        <v>0.114690489768982</v>
       </c>
       <c r="H37" t="n">
-        <v>-7.367514030726398</v>
+        <v>-7.375594197362187</v>
       </c>
       <c r="I37" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>2019</v>
       </c>
       <c r="C38" t="n">
-        <v>1.750871300697327</v>
+        <v>1.739336371421814</v>
       </c>
       <c r="D38" t="n">
         <v>1.624</v>
@@ -1795,16 +1795,16 @@
         <v>1.734</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1268713006973266</v>
+        <v>-0.1153363714218139</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1268713006973266</v>
+        <v>0.1153363714218139</v>
       </c>
       <c r="H38" t="n">
-        <v>-7.812272210426512</v>
+        <v>-7.101993314151099</v>
       </c>
       <c r="I38" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>2019</v>
       </c>
       <c r="C39" t="n">
-        <v>1.364792943000793</v>
+        <v>1.355835199356079</v>
       </c>
       <c r="D39" t="n">
         <v>1.279</v>
@@ -1831,16 +1831,16 @@
         <v>1.389</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.08579294300079354</v>
+        <v>-0.07683519935607919</v>
       </c>
       <c r="G39" t="n">
-        <v>0.08579294300079354</v>
+        <v>0.07683519935607919</v>
       </c>
       <c r="H39" t="n">
-        <v>-6.707814151743046</v>
+        <v>-6.007443264744268</v>
       </c>
       <c r="I39" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>2019</v>
       </c>
       <c r="C40" t="n">
-        <v>1.325121998786926</v>
+        <v>1.32889986038208</v>
       </c>
       <c r="D40" t="n">
         <v>1.274</v>
@@ -1867,16 +1867,16 @@
         <v>1.356</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.05112199878692625</v>
+        <v>-0.05489986038208006</v>
       </c>
       <c r="G40" t="n">
-        <v>0.05112199878692625</v>
+        <v>0.05489986038208006</v>
       </c>
       <c r="H40" t="n">
-        <v>-4.012715760355279</v>
+        <v>-4.30925120738462</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>2019</v>
       </c>
       <c r="C41" t="n">
-        <v>1.722007155418396</v>
+        <v>1.728291988372803</v>
       </c>
       <c r="D41" t="n">
         <v>1.589</v>
@@ -1903,16 +1903,16 @@
         <v>1.699</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.133007155418396</v>
+        <v>-0.1392919883728028</v>
       </c>
       <c r="G41" t="n">
-        <v>0.133007155418396</v>
+        <v>0.1392919883728028</v>
       </c>
       <c r="H41" t="n">
-        <v>-8.370494362391192</v>
+        <v>-8.766015630761659</v>
       </c>
       <c r="I41" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>2019</v>
       </c>
       <c r="C42" t="n">
-        <v>1.578067302703857</v>
+        <v>1.586137533187866</v>
       </c>
       <c r="D42" t="n">
         <v>1.46</v>
@@ -1939,16 +1939,16 @@
         <v>1.552</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1180673027038575</v>
+        <v>-0.1261375331878662</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1180673027038575</v>
+        <v>0.1261375331878662</v>
       </c>
       <c r="H42" t="n">
-        <v>-8.086801555058729</v>
+        <v>-8.639557067662071</v>
       </c>
       <c r="I42" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>2019</v>
       </c>
       <c r="C43" t="n">
-        <v>1.525238156318665</v>
+        <v>1.544357895851135</v>
       </c>
       <c r="D43" t="n">
         <v>1.474</v>
@@ -1975,16 +1975,16 @@
         <v>1.566</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.05123815631866457</v>
+        <v>-0.07035789585113528</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05123815631866457</v>
+        <v>0.07035789585113528</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.476130008050514</v>
+        <v>-4.773262947838215</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>2019</v>
       </c>
       <c r="C44" t="n">
-        <v>1.331811189651489</v>
+        <v>1.303607106208801</v>
       </c>
       <c r="D44" t="n">
         <v>1.253</v>
@@ -2011,16 +2011,16 @@
         <v>1.35</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.07881118965148937</v>
+        <v>-0.05060710620880138</v>
       </c>
       <c r="G44" t="n">
-        <v>0.07881118965148937</v>
+        <v>0.05060710620880138</v>
       </c>
       <c r="H44" t="n">
-        <v>-6.289799652952064</v>
+        <v>-4.038875196233151</v>
       </c>
       <c r="I44" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>2019</v>
       </c>
       <c r="C45" t="n">
-        <v>2.384911298751831</v>
+        <v>2.372434616088867</v>
       </c>
       <c r="D45" t="n">
         <v>2.185</v>
@@ -2047,13 +2047,13 @@
         <v>2.413</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.199911298751831</v>
+        <v>-0.1874346160888671</v>
       </c>
       <c r="G45" t="n">
-        <v>0.199911298751831</v>
+        <v>0.1874346160888671</v>
       </c>
       <c r="H45" t="n">
-        <v>-9.149258524111259</v>
+        <v>-8.578243299261654</v>
       </c>
       <c r="I45" t="n">
         <v>82</v>
@@ -2074,7 +2074,7 @@
         <v>2019</v>
       </c>
       <c r="C46" t="n">
-        <v>1.649275302886963</v>
+        <v>1.634228706359863</v>
       </c>
       <c r="D46" t="n">
         <v>1.497</v>
@@ -2083,16 +2083,16 @@
         <v>1.632</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1522753028869628</v>
+        <v>-0.1372287063598632</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1522753028869628</v>
+        <v>0.1372287063598632</v>
       </c>
       <c r="H46" t="n">
-        <v>-10.1720309209728</v>
+        <v>-9.16691425249587</v>
       </c>
       <c r="I46" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>2019</v>
       </c>
       <c r="C47" t="n">
-        <v>2.015995740890503</v>
+        <v>2.006878137588501</v>
       </c>
       <c r="D47" t="n">
         <v>1.854</v>
@@ -2119,16 +2119,16 @@
         <v>2.007</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1619957408905028</v>
+        <v>-0.1528781375885009</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1619957408905028</v>
+        <v>0.1528781375885009</v>
       </c>
       <c r="H47" t="n">
-        <v>-8.737634352238556</v>
+        <v>-8.245854238861968</v>
       </c>
       <c r="I47" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>2019</v>
       </c>
       <c r="C48" t="n">
-        <v>1.821627736091614</v>
+        <v>1.822575092315674</v>
       </c>
       <c r="D48" t="n">
         <v>1.788</v>
@@ -2155,16 +2155,16 @@
         <v>1.843</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.03362773609161374</v>
+        <v>-0.03457509231567379</v>
       </c>
       <c r="G48" t="n">
-        <v>0.03362773609161374</v>
+        <v>0.03457509231567379</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.88074586642135</v>
+        <v>-1.933729995283769</v>
       </c>
       <c r="I48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>2019</v>
       </c>
       <c r="C49" t="n">
-        <v>1.896326780319214</v>
+        <v>1.903397917747498</v>
       </c>
       <c r="D49" t="n">
         <v>1.96</v>
@@ -2191,16 +2191,16 @@
         <v>1.93</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0636732196807861</v>
+        <v>0.05660208225250241</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0636732196807861</v>
+        <v>0.05660208225250241</v>
       </c>
       <c r="H49" t="n">
-        <v>3.248633657182964</v>
+        <v>2.887861339413388</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>2019</v>
       </c>
       <c r="C50" t="n">
-        <v>1.584894895553589</v>
+        <v>1.593846917152405</v>
       </c>
       <c r="D50" t="n">
         <v>1.537</v>
@@ -2227,20 +2227,20 @@
         <v>1.6</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.04789489555358895</v>
+        <v>-0.05684691715240486</v>
       </c>
       <c r="G50" t="n">
-        <v>0.04789489555358895</v>
+        <v>0.05684691715240486</v>
       </c>
       <c r="H50" t="n">
-        <v>-3.116128533089717</v>
+        <v>-3.69856324999381</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Отличная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
         <v>2019</v>
       </c>
       <c r="C51" t="n">
-        <v>1.714060187339783</v>
+        <v>1.700549125671387</v>
       </c>
       <c r="D51" t="n">
         <v>1.631</v>
@@ -2263,16 +2263,16 @@
         <v>1.698</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.08306018733978271</v>
+        <v>-0.06954912567138671</v>
       </c>
       <c r="G51" t="n">
-        <v>0.08306018733978271</v>
+        <v>0.06954912567138671</v>
       </c>
       <c r="H51" t="n">
-        <v>-5.092592724695446</v>
+        <v>-4.26420145134192</v>
       </c>
       <c r="I51" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>2019</v>
       </c>
       <c r="C52" t="n">
-        <v>1.696268558502197</v>
+        <v>1.691432476043701</v>
       </c>
       <c r="D52" t="n">
         <v>1.63</v>
@@ -2299,13 +2299,13 @@
         <v>1.668</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.06626855850219737</v>
+        <v>-0.06143247604370128</v>
       </c>
       <c r="G52" t="n">
-        <v>0.06626855850219737</v>
+        <v>0.06143247604370128</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.065555736331127</v>
+        <v>-3.768863560963269</v>
       </c>
       <c r="I52" t="n">
         <v>29</v>
@@ -2326,7 +2326,7 @@
         <v>2019</v>
       </c>
       <c r="C53" t="n">
-        <v>1.591783046722412</v>
+        <v>1.592536330223083</v>
       </c>
       <c r="D53" t="n">
         <v>1.546</v>
@@ -2335,13 +2335,13 @@
         <v>1.603</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.04578304672241207</v>
+        <v>-0.04653633022308346</v>
       </c>
       <c r="G53" t="n">
-        <v>0.04578304672241207</v>
+        <v>0.04653633022308346</v>
       </c>
       <c r="H53" t="n">
-        <v>-2.961387239483316</v>
+        <v>-3.010111916111478</v>
       </c>
       <c r="I53" t="n">
         <v>14</v>
@@ -2362,7 +2362,7 @@
         <v>2019</v>
       </c>
       <c r="C54" t="n">
-        <v>1.626326084136963</v>
+        <v>1.602830290794373</v>
       </c>
       <c r="D54" t="n">
         <v>1.496</v>
@@ -2371,16 +2371,16 @@
         <v>1.601</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1303260841369629</v>
+        <v>-0.1068302907943726</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1303260841369629</v>
+        <v>0.1068302907943726</v>
       </c>
       <c r="H54" t="n">
-        <v>-8.711636640171317</v>
+        <v>-7.141062218875172</v>
       </c>
       <c r="I54" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>1.229163646697998</v>
+        <v>1.249510765075684</v>
       </c>
       <c r="D55" t="n">
         <v>1.188</v>
@@ -2407,20 +2407,20 @@
         <v>1.268</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0411636466979981</v>
+        <v>-0.06151076507568365</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0411636466979981</v>
+        <v>0.06151076507568365</v>
       </c>
       <c r="H55" t="n">
-        <v>-3.464953425757416</v>
+        <v>-5.1776738279195</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Отличная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
         <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>1.824081778526306</v>
+        <v>1.822159767150879</v>
       </c>
       <c r="D56" t="n">
         <v>1.773</v>
@@ -2443,20 +2443,20 @@
         <v>1.844</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.05108177852630624</v>
+        <v>-0.049159767150879</v>
       </c>
       <c r="G56" t="n">
-        <v>0.05108177852630624</v>
+        <v>0.049159767150879</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.881092979487098</v>
+        <v>-2.772688502587648</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Отличная</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
         <v>2019</v>
       </c>
       <c r="C57" t="n">
-        <v>1.762584209442139</v>
+        <v>1.766700506210327</v>
       </c>
       <c r="D57" t="n">
         <v>1.71</v>
@@ -2479,13 +2479,13 @@
         <v>1.791</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.05258420944213871</v>
+        <v>-0.05670050621032718</v>
       </c>
       <c r="G57" t="n">
-        <v>0.05258420944213871</v>
+        <v>0.05670050621032718</v>
       </c>
       <c r="H57" t="n">
-        <v>-3.075099967376532</v>
+        <v>-3.315819076627321</v>
       </c>
       <c r="I57" t="n">
         <v>24</v>
@@ -2506,7 +2506,7 @@
         <v>2019</v>
       </c>
       <c r="C58" t="n">
-        <v>1.601615786552429</v>
+        <v>1.601464152336121</v>
       </c>
       <c r="D58" t="n">
         <v>1.52</v>
@@ -2515,16 +2515,16 @@
         <v>1.597</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.08161578655242918</v>
+        <v>-0.08146415233612059</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08161578655242918</v>
+        <v>0.08146415233612059</v>
       </c>
       <c r="H58" t="n">
-        <v>-5.369459641607182</v>
+        <v>-5.359483706323723</v>
       </c>
       <c r="I58" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>2019</v>
       </c>
       <c r="C59" t="n">
-        <v>2.873488426208496</v>
+        <v>2.869140148162842</v>
       </c>
       <c r="D59" t="n">
         <v>2.559</v>
@@ -2551,13 +2551,13 @@
         <v>2.798</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3144884262084959</v>
+        <v>-0.3101401481628416</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3144884262084959</v>
+        <v>0.3101401481628416</v>
       </c>
       <c r="H59" t="n">
-        <v>-12.28950473655709</v>
+        <v>-12.11958375001335</v>
       </c>
       <c r="I59" t="n">
         <v>84</v>
@@ -2578,7 +2578,7 @@
         <v>2019</v>
       </c>
       <c r="C60" t="n">
-        <v>1.69749653339386</v>
+        <v>1.711808562278748</v>
       </c>
       <c r="D60" t="n">
         <v>1.579</v>
@@ -2587,16 +2587,16 @@
         <v>1.687</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1184965333938599</v>
+        <v>-0.1328085622787476</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1184965333938599</v>
+        <v>0.1328085622787476</v>
       </c>
       <c r="H60" t="n">
-        <v>-7.504530297267885</v>
+        <v>-8.41092858003468</v>
       </c>
       <c r="I60" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>2019</v>
       </c>
       <c r="C61" t="n">
-        <v>1.383531451225281</v>
+        <v>1.369851231575012</v>
       </c>
       <c r="D61" t="n">
         <v>1.323</v>
@@ -2623,20 +2623,20 @@
         <v>1.393</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.06053145122528081</v>
+        <v>-0.04685123157501225</v>
       </c>
       <c r="G61" t="n">
-        <v>0.06053145122528081</v>
+        <v>0.04685123157501225</v>
       </c>
       <c r="H61" t="n">
-        <v>-4.575317552931278</v>
+        <v>-3.541287345050057</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Отличная</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>2019</v>
       </c>
       <c r="C62" t="n">
-        <v>1.436242461204529</v>
+        <v>1.392086505889893</v>
       </c>
       <c r="D62" t="n">
         <v>1.345</v>
@@ -2659,20 +2659,20 @@
         <v>1.443</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.09124246120452884</v>
+        <v>-0.0470865058898926</v>
       </c>
       <c r="G62" t="n">
-        <v>0.09124246120452884</v>
+        <v>0.0470865058898926</v>
       </c>
       <c r="H62" t="n">
-        <v>-6.78382611186088</v>
+        <v>-3.500855456497592</v>
       </c>
       <c r="I62" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Отличная</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
         <v>2019</v>
       </c>
       <c r="C63" t="n">
-        <v>1.475231289863586</v>
+        <v>1.491728544235229</v>
       </c>
       <c r="D63" t="n">
         <v>1.396</v>
@@ -2695,16 +2695,16 @@
         <v>1.498</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.07923128986358652</v>
+        <v>-0.09572854423522958</v>
       </c>
       <c r="G63" t="n">
-        <v>0.07923128986358652</v>
+        <v>0.09572854423522958</v>
       </c>
       <c r="H63" t="n">
-        <v>-5.675593829769808</v>
+        <v>-6.857345575589512</v>
       </c>
       <c r="I63" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>2019</v>
       </c>
       <c r="C64" t="n">
-        <v>1.305558443069458</v>
+        <v>1.337677955627441</v>
       </c>
       <c r="D64" t="n">
         <v>1.235</v>
@@ -2731,20 +2731,20 @@
         <v>1.319</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.07055844306945791</v>
+        <v>-0.1026779556274413</v>
       </c>
       <c r="G64" t="n">
-        <v>0.07055844306945791</v>
+        <v>0.1026779556274413</v>
       </c>
       <c r="H64" t="n">
-        <v>-5.713234256636268</v>
+        <v>-8.314004504246258</v>
       </c>
       <c r="I64" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Удовлетворительная</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
         <v>2019</v>
       </c>
       <c r="C65" t="n">
-        <v>1.891048789024353</v>
+        <v>1.881678819656372</v>
       </c>
       <c r="D65" t="n">
         <v>1.877</v>
@@ -2767,16 +2767,16 @@
         <v>1.876</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.01404878902435303</v>
+        <v>-0.004678819656372069</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01404878902435303</v>
+        <v>0.004678819656372069</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.74847037956063</v>
+        <v>-0.2492711591034666</v>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>2019</v>
       </c>
       <c r="C66" t="n">
-        <v>1.728730797767639</v>
+        <v>1.724454998970032</v>
       </c>
       <c r="D66" t="n">
         <v>1.614</v>
@@ -2803,16 +2803,16 @@
         <v>1.702</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1147307977676391</v>
+        <v>-0.1104549989700316</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1147307977676391</v>
+        <v>0.1104549989700316</v>
       </c>
       <c r="H66" t="n">
-        <v>-7.108475698118901</v>
+        <v>-6.843556317845826</v>
       </c>
       <c r="I66" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>2019</v>
       </c>
       <c r="C67" t="n">
-        <v>1.319879055023193</v>
+        <v>1.319323539733887</v>
       </c>
       <c r="D67" t="n">
         <v>1.234</v>
@@ -2839,13 +2839,13 @@
         <v>1.303</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.08587905502319337</v>
+        <v>-0.08532353973388673</v>
       </c>
       <c r="G67" t="n">
-        <v>0.08587905502319337</v>
+        <v>0.08532353973388673</v>
       </c>
       <c r="H67" t="n">
-        <v>-6.959404783078879</v>
+        <v>-6.91438733661967</v>
       </c>
       <c r="I67" t="n">
         <v>49</v>
@@ -2866,7 +2866,7 @@
         <v>2019</v>
       </c>
       <c r="C68" t="n">
-        <v>1.446207642555237</v>
+        <v>1.442116856575012</v>
       </c>
       <c r="D68" t="n">
         <v>1.348</v>
@@ -2875,16 +2875,16 @@
         <v>1.445</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.09820764255523673</v>
+        <v>-0.09411685657501212</v>
       </c>
       <c r="G68" t="n">
-        <v>0.09820764255523673</v>
+        <v>0.09411685657501212</v>
       </c>
       <c r="H68" t="n">
-        <v>-7.285433423978985</v>
+        <v>-6.98196265393265</v>
       </c>
       <c r="I68" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>2019</v>
       </c>
       <c r="C69" t="n">
-        <v>1.278863906860352</v>
+        <v>1.291104435920715</v>
       </c>
       <c r="D69" t="n">
         <v>1.283</v>
@@ -2911,16 +2911,16 @@
         <v>1.315</v>
       </c>
       <c r="F69" t="n">
-        <v>0.004136093139648356</v>
+        <v>-0.008104435920715414</v>
       </c>
       <c r="G69" t="n">
-        <v>0.004136093139648356</v>
+        <v>0.008104435920715414</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3223767061300356</v>
+        <v>-0.6316785596816379</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>2019</v>
       </c>
       <c r="C70" t="n">
-        <v>1.442649245262146</v>
+        <v>1.422619462013245</v>
       </c>
       <c r="D70" t="n">
         <v>1.411</v>
@@ -2947,16 +2947,16 @@
         <v>1.473</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.03164924526214596</v>
+        <v>-0.0116194620132446</v>
       </c>
       <c r="G70" t="n">
-        <v>0.03164924526214596</v>
+        <v>0.0116194620132446</v>
       </c>
       <c r="H70" t="n">
-        <v>-2.24303651751566</v>
+        <v>-0.8234912837168389</v>
       </c>
       <c r="I70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>2019</v>
       </c>
       <c r="C71" t="n">
-        <v>1.399879813194275</v>
+        <v>1.388004064559937</v>
       </c>
       <c r="D71" t="n">
         <v>1.345</v>
@@ -2983,20 +2983,20 @@
         <v>1.426</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.05487981319427493</v>
+        <v>-0.04300406455993655</v>
       </c>
       <c r="G71" t="n">
-        <v>0.05487981319427493</v>
+        <v>0.04300406455993655</v>
       </c>
       <c r="H71" t="n">
-        <v>-4.080283508868025</v>
+        <v>-3.197328220069632</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Отличная</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
         <v>2019</v>
       </c>
       <c r="C72" t="n">
-        <v>1.306665778160095</v>
+        <v>1.315173149108887</v>
       </c>
       <c r="D72" t="n">
         <v>1.22</v>
@@ -3019,16 +3019,16 @@
         <v>1.304</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.08666577816009524</v>
+        <v>-0.09517314910888675</v>
       </c>
       <c r="G72" t="n">
-        <v>0.08666577816009524</v>
+        <v>0.09517314910888675</v>
       </c>
       <c r="H72" t="n">
-        <v>-7.103752308204528</v>
+        <v>-7.801077795810389</v>
       </c>
       <c r="I72" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>2019</v>
       </c>
       <c r="C73" t="n">
-        <v>1.803409934043884</v>
+        <v>1.803331613540649</v>
       </c>
       <c r="D73" t="n">
         <v>1.715</v>
@@ -3055,16 +3055,16 @@
         <v>1.809</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.0884099340438842</v>
+        <v>-0.08833161354064933</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0884099340438842</v>
+        <v>0.08833161354064933</v>
       </c>
       <c r="H73" t="n">
-        <v>-5.15509819497867</v>
+        <v>-5.150531401787133</v>
       </c>
       <c r="I73" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>2019</v>
       </c>
       <c r="C74" t="n">
-        <v>1.646140933036804</v>
+        <v>1.632277131080627</v>
       </c>
       <c r="D74" t="n">
         <v>1.494</v>
@@ -3091,16 +3091,16 @@
         <v>1.633</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1521409330368042</v>
+        <v>-0.1382771310806274</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1521409330368042</v>
+        <v>0.1382771310806274</v>
       </c>
       <c r="H74" t="n">
-        <v>-10.18346272000028</v>
+        <v>-9.255497394954983</v>
       </c>
       <c r="I74" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>2019</v>
       </c>
       <c r="C75" t="n">
-        <v>1.513417601585388</v>
+        <v>1.485681653022766</v>
       </c>
       <c r="D75" t="n">
         <v>1.425</v>
@@ -3127,16 +3127,16 @@
         <v>1.511</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.08841760158538814</v>
+        <v>-0.06068165302276607</v>
       </c>
       <c r="G75" t="n">
-        <v>0.08841760158538814</v>
+        <v>0.06068165302276607</v>
       </c>
       <c r="H75" t="n">
-        <v>-6.20474397090443</v>
+        <v>-4.258361615632706</v>
       </c>
       <c r="I75" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>2019</v>
       </c>
       <c r="C76" t="n">
-        <v>1.581681489944458</v>
+        <v>1.571240782737732</v>
       </c>
       <c r="D76" t="n">
         <v>1.564</v>
@@ -3163,16 +3163,16 @@
         <v>1.575</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.01768148994445795</v>
+        <v>-0.007240782737731877</v>
       </c>
       <c r="G76" t="n">
-        <v>0.01768148994445795</v>
+        <v>0.007240782737731877</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.130530047599613</v>
+        <v>-0.4629656481925752</v>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>2019</v>
       </c>
       <c r="C77" t="n">
-        <v>1.804262161254883</v>
+        <v>1.802600383758545</v>
       </c>
       <c r="D77" t="n">
         <v>1.695</v>
@@ -3199,16 +3199,16 @@
         <v>1.795</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.1092621612548828</v>
+        <v>-0.1076003837585449</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1092621612548828</v>
+        <v>0.1076003837585449</v>
       </c>
       <c r="H77" t="n">
-        <v>-6.446145206777743</v>
+        <v>-6.348105236492321</v>
       </c>
       <c r="I77" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>2019</v>
       </c>
       <c r="C78" t="n">
-        <v>1.571159958839417</v>
+        <v>1.584847331047058</v>
       </c>
       <c r="D78" t="n">
         <v>1.474</v>
@@ -3235,20 +3235,20 @@
         <v>1.565</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.09715995883941653</v>
+        <v>-0.1108473310470581</v>
       </c>
       <c r="G78" t="n">
-        <v>0.09715995883941653</v>
+        <v>0.1108473310470581</v>
       </c>
       <c r="H78" t="n">
-        <v>-6.591584724519439</v>
+        <v>-7.520171712826196</v>
       </c>
       <c r="I78" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Хорошая</t>
+          <t>Удовлетворительная</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
         <v>2019</v>
       </c>
       <c r="C79" t="n">
-        <v>2.6979660987854</v>
+        <v>2.695426940917969</v>
       </c>
       <c r="D79" t="n">
         <v>2.602</v>
@@ -3271,16 +3271,16 @@
         <v>2.622</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.09596609878540052</v>
+        <v>-0.09342694091796888</v>
       </c>
       <c r="G79" t="n">
-        <v>0.09596609878540052</v>
+        <v>0.09342694091796888</v>
       </c>
       <c r="H79" t="n">
-        <v>-3.688166748093794</v>
+        <v>-3.590581895386967</v>
       </c>
       <c r="I79" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>2019</v>
       </c>
       <c r="C80" t="n">
-        <v>1.621384978294373</v>
+        <v>1.640234351158142</v>
       </c>
       <c r="D80" t="n">
         <v>1.495</v>
@@ -3307,16 +3307,16 @@
         <v>1.616</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.1263849782943725</v>
+        <v>-0.145234351158142</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1263849782943725</v>
+        <v>0.145234351158142</v>
       </c>
       <c r="H80" t="n">
-        <v>-8.453844701964712</v>
+        <v>-9.714672318270367</v>
       </c>
       <c r="I80" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>2019</v>
       </c>
       <c r="C81" t="n">
-        <v>1.949250817298889</v>
+        <v>1.937755227088928</v>
       </c>
       <c r="D81" t="n">
         <v>1.617</v>
@@ -3343,13 +3343,13 @@
         <v>1.943</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.3322508172988892</v>
+        <v>-0.3207552270889282</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3322508172988892</v>
+        <v>0.3207552270889282</v>
       </c>
       <c r="H81" t="n">
-        <v>-20.54736037717311</v>
+        <v>-19.83643952312481</v>
       </c>
       <c r="I81" t="n">
         <v>85</v>
@@ -3370,7 +3370,7 @@
         <v>2019</v>
       </c>
       <c r="C82" t="n">
-        <v>1.839759707450867</v>
+        <v>1.836670398712158</v>
       </c>
       <c r="D82" t="n">
         <v>1.805</v>
@@ -3379,13 +3379,13 @@
         <v>1.867</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.03475970745086676</v>
+        <v>-0.03167039871215827</v>
       </c>
       <c r="G82" t="n">
-        <v>0.03475970745086676</v>
+        <v>0.03167039871215827</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.925745565144973</v>
+        <v>-1.754592726435361</v>
       </c>
       <c r="I82" t="n">
         <v>10</v>
@@ -3406,7 +3406,7 @@
         <v>2019</v>
       </c>
       <c r="C83" t="n">
-        <v>1.438763499259949</v>
+        <v>1.487430453300476</v>
       </c>
       <c r="D83" t="n">
         <v>1.395</v>
@@ -3415,20 +3415,20 @@
         <v>1.484</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.04376349925994871</v>
+        <v>-0.09243045330047606</v>
       </c>
       <c r="G83" t="n">
-        <v>0.04376349925994871</v>
+        <v>0.09243045330047606</v>
       </c>
       <c r="H83" t="n">
-        <v>-3.13716840573109</v>
+        <v>-6.625838946270685</v>
       </c>
       <c r="I83" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Отличная</t>
+          <t>Хорошая</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
         <v>2019</v>
       </c>
       <c r="C84" t="n">
-        <v>1.357545971870422</v>
+        <v>1.346568584442139</v>
       </c>
       <c r="D84" t="n">
         <v>1.43</v>
@@ -3451,16 +3451,16 @@
         <v>1.365</v>
       </c>
       <c r="F84" t="n">
-        <v>0.07245402812957757</v>
+        <v>0.08343141555786127</v>
       </c>
       <c r="G84" t="n">
-        <v>0.07245402812957757</v>
+        <v>0.08343141555786127</v>
       </c>
       <c r="H84" t="n">
-        <v>5.066715253816613</v>
+        <v>5.834364724325963</v>
       </c>
       <c r="I84" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>1.426281929016113</v>
+        <v>1.421564102172852</v>
       </c>
       <c r="D85" t="n">
         <v>1.35</v>
@@ -3487,16 +3487,16 @@
         <v>1.432</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.07628192901611319</v>
+        <v>-0.07156410217285147</v>
       </c>
       <c r="G85" t="n">
-        <v>0.07628192901611319</v>
+        <v>0.07156410217285147</v>
       </c>
       <c r="H85" t="n">
-        <v>-5.650513260452829</v>
+        <v>-5.301044605396405</v>
       </c>
       <c r="I85" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>2019</v>
       </c>
       <c r="C86" t="n">
-        <v>1.252685070037842</v>
+        <v>1.254064202308655</v>
       </c>
       <c r="D86" t="n">
         <v>1.136</v>
@@ -3523,16 +3523,16 @@
         <v>1.228</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.1166850700378419</v>
+        <v>-0.1180642023086549</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1166850700378419</v>
+        <v>0.1180642023086549</v>
       </c>
       <c r="H86" t="n">
-        <v>-10.27157306671143</v>
+        <v>-10.39297555533934</v>
       </c>
       <c r="I86" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
